--- a/Phase6.2/quantized (Cleaned)/load_56.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_56.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8720"/>
+    <workbookView windowWidth="18350" windowHeight="8720"/>
   </bookViews>
   <sheets>
     <sheet name="Timestamp logs" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,6 +696,9379 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Sensing Unit Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$A$1:$A$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>26.0286</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.2879</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.815</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.1779</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21.4594</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.203</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.9061</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.9603</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37.2243</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25.8236</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24.2978</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36.4077</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.6027</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39.1379</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>38.9755</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21.2108</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18.2427</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30.6376</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24.3104</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>37.3771</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>33.9021</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23.7013</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>40.6121</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.7324</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25.475</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>49.5128</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>20.031</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>25.5863</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>40.37</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>18.5001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>32.6318</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>25.7165</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>15.9072</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>20.6558</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>23.0461</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>16.9532</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>14.3155</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>23.4843</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>34.4618</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>15.4216</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>15.8694</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>25.0033</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>156.9572</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>54.6591</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>28.8848</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>16.2139</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>21.7489</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>39.5873</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>20.4626</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>19.1058</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>16.137</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>18.9045</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>17.8482</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>17.8408</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>22.1859</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>32.6444</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>19.422</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>18.622</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>27.1849</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>30.1442</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17.0932</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>21.2531</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>29.9385</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>18.5747</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>29.1884</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.1818</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>16.6217</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>15.9994</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.6621</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>44.0449</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>16.0892</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>23.2218</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>28.1587</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>25.9915</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>40.6756</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>49.8971</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>16.8572</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>23.2279</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>20.213</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>22.9504</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>29.5043</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>16.8694</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>41.0813</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>17.7331</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>31.6044</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>32.6604</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>36.7969</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>34.2128</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>15.9217</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>13.6974</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>24.0772</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>15.4135</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>27.2096</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>19.4097</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>41.4314</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>13.5219</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>21.8579</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46.1409</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>17.8654</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>16.9714</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>17.7102</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>16.1309</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>132.2616</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>47.8516</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>14.6313</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>36.7774</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>18.2558</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>16.361</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>16.7782</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>14.9263</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>28.9531</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>33.4999</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>15.9445</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>38.1833</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>32.9988</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>31.7454</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>27.8009</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>16.6556</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>46.3732</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>20.229</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>16.5757</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>34.9491</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>37.4428</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>27.6826</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>35.2944</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>14.7375</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>27.0986</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>17.4645</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>40.0441</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>18.8927</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>25.3746</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>28.8945</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>22.2812</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>33.8895</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>30.2236</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>17.0643</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>24.324</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>14.9391</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>30.7196</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>13.4955</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>26.4032</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>33.4711</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>31.973</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>15.2245</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>15.4627</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>19.1393</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>17.5893</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>25.4577</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>140.1381</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>20.4405</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>23.4078</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>35.5153</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>15.2082</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>17.6696</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>18.7398</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>28.109</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>18.0589</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>34.8189</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>166.4999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>39.4844</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>30.3285</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>25.561</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>31.216</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>42.1919</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>29.0642</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>18.4516</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>44.7403</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>46.9418</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>18.9746</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>20.703</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>21.4797</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>29.9157</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>15.0474</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>29.5648</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>33.5314</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>20.0013</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>14.3977</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>43.2024</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>17.0638</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>25.8129</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>17.4105</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>42.5517</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>15.8572</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>22.9767</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>15.6172</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>49.2453</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>29.7492</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>20.0475</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>25.03</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>16.9122</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>19.3063</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>42.7152</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>18.7434</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>18.2325</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>15.6375</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>24.6385</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>18.1021</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>19.7082</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>16.3404</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>30.7941</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>37.6262</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>16.2308</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>29.1863</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>27.847</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>30.0558</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>22.8185</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>62.9943</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>26.7494</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>20.3032</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>42.045</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>19.5562</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>24.1859</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>12.3679</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>12.8524</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>20.0262</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>20.5767</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>14.8514</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>13.6037</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>23.4321</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>13.4755</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>20.0833</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>17.3263</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>12.4979</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>11.4298</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>19.909</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>19.2322</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>21.7749</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>22.3924</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>15.1698</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>27.5367</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>48.1223</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>23.2532</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>15.0102</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>15.7809</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>16.7519</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>19.6937</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>16.3818</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>27.1476</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>23.0208</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>24.9203</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>15.5317</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>29.4442</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>16.4683</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>30.2245</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>16.2042</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>20.5862</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>16.0142</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>15.5688</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>20.4993</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>18.7414</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>24.4844</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>75.2594</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>43.2143</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>17.2754</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>15.2098</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>27.038</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>37.5203</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>16.022</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>18.0823</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>28.9859</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>20.1113</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>20.8777</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>27.3456</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>37.036</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>27.5527</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>44.8779</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>32.5085</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>26.249</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>17.505</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>47.8805</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>42.8977</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>23.3666</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>28.8043</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>37.6734</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>16.2742</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>28.0321</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>26.0042</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>129.5887</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>19.4232</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>29.8682</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>16.7885</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>33.8565</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>22.489</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>24.8644</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>16.7299</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>34.1753</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>41.3696</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>19.4364</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>16.398</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>16.0974</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>29.2502</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>21.4221</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>135.5026</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>19.0016</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>32.5425</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>17.3477</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>29.6868</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>16.9367</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>49.8389</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>16.7134</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>18.5557</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>31.3543</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>34.6724</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>20.6402</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>21.4352</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>20.9155</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>29.7896</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>15.8546</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>27.8276</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>17.1346</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>39.5934</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>17.2089</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>16.3338</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>31.3909</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>27.1776</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>18.2089</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>15.7076</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>24.9935</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>24.0487</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>31.3104</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>15.7832</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>33.3825</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>15.2703</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>18.8096</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>18.1399</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>26.4175</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>16.7364</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>16.82</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>26.592</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>18.2143</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>24.6613</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>17.5962</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>17.8608</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>23.4664</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>28.2963</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>16.3835</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>32.6912</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>17.616</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>23.6609</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>16.0683</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>38.1116</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>37.1546</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>16.1904</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>19.106</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>16.6045</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>22.761</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>21.6918</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>21.9236</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>17.7762</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>35.6185</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>18.5179</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>44.8418</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>16.347</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>22.9898</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>18.3487</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>20.0571</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>24.9267</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>42.6258</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>26.3601</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>21.2213</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>16.0496</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>43.6497</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>42.4287</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>33.1876</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>28.7366</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>15.4549</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>32.0703</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>14.4354</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>28.2556</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>15.3415</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>27.8504</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>18.7386</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>14.9808</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>23.8999</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>17.206</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>28.1071</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>15.1358</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>16.9795</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>13.0782</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>36.0171</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>10.7045</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>26.2516</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>22.3943</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>19.6412</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>33.2363</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>9.9031</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>9.3473</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>11.6529</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>22.2525</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>16.4256</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>11.3115</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>24.7198</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>14.1644</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>15.578</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>22.315</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>10.5897</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>19.3125</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>12.2543</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>9.5899</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>21.9599</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>9.2828</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>10.8205</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>16.9242</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>13.4394</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>10.5757</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>22.0969</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>9.7348</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>15.573</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>16.466</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>13.7011</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>14.0269</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>18.2485</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>14.0559</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>20.1715</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>10.1069</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>13.5215</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>13.7986</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>49.2656</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>17.4472</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>17.7542</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>41.3383</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>17.3211</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>19.4732</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>28.7071</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>20.8412</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>26.0871</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>21.8411</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>12.7371</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>16.5918</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>15.4421</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>24.1101</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>15.2891</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>18.046</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>19.6158</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>14.0733</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>19.3738</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>124.5155</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>10.9149</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>13.9416</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>19.5963</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>20.1427</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>27.5633</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>16.6928</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>24.5535</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>9.6237</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>93.9547</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>12.7952</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>12.2243</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>15.6549</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>13.1481</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>12.2473</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>16.3481</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>21.9253</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>10.5999</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>9.1545</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>10.7787</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>14.89</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>16.9511</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>9.3711</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>11.1727</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>19.6576</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>9.6505</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>10.9502</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>9.5902</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>11.2703</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>11.2666</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>14.8983</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>11.3405</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>23.5755</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>10.4373</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>11.4068</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>23.6759</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>12.7222</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>9.6619</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>19.4882</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>10.8117</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>11.3132</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>13.7731</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>10.5057</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>12.8197</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>11.8918</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>14.3834</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>19.2666</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>26.3739</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>28.2134</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>19.4606</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>21.929</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>12.1947</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>13.4117</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>9.0405</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>18.9066</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>14.0484</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>23.3538</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>15.6311</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>11.1192</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>24.8014</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>12.6672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="694275946"/>
+        <c:axId val="528344648"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="694275946"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="528344648"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="528344648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="694275946"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Queue Lifetime: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$B$1:$B$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>1.742455</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.824543</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.133655</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.767354</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>308.376217</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>398.833702</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>485.428978</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>589.094808</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>597.188117</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>647.562591</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>676.406419</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>661.818176</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>849.623084</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1069.845094</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1059.533045</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1065.108999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1084.565665</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1164.701904</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1253.883243</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1415.332207</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1328.573796</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1357.23793</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1379.33113</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1464.610825</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1590.007999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1597.269109</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1658.552688</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1830.719888</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1844.81573</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1846.272452</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1839.788309</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2034.567794</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2163.033078</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2149.485579</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2214.403926</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2334.347909</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2462.242799</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2450.663601</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2683.379746</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2758.192101</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2868.402021</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2829.882099</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2724.45269</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2767.962896</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3059.653755</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2984.472176</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3193.26402</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3190.29918</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3173.403216</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3310.82506</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3306.883481</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3305.944226</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3634.25983</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3761.622272</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3732.611017</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3669.896375</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3787.562032</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4041.805703</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3967.470627</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3937.421518</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4071.202288</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4121.201192</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4316.523525</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>4351.415579</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4435.229778</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4615.781105</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4586.97122</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4744.808608</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4816.858976</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4845.478727</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4935.014264</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5081.73219</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5012.827416</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5027.186871</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5094.415199</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4970.217271</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4985.966034</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5057.424191</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5062.763068</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5167.694639</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5080.896907</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5055.3954</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5074.803085</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5072.960852</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5046.30252</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5257.915561</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5336.529249</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5113.120673</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5138.632011</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4949.430434</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5125.81756</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5054.710224</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5042.088952</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5060.693935</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5257.191597</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4960.058227</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5041.576086</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5094.007844</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5084.907874</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5200.762912</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5216.26991</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4922.89248</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4925.730846</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4890.829171</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4939.737048</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4963.946095</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4935.257524</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4966.972374</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5016.348128</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4881.483959</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4905.703591</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4827.631701</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4960.047369</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5026.099588</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4889.682099</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4878.648244</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4901.265268</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4979.913744</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4889.917906</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4913.260524</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4866.311172</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5022.462824</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4980.382231</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4916.998789</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4643.636986</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4517.835796</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4596.871726</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4791.777055</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4599.717104</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4662.555094</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4618.797452</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4637.559359</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4646.327447</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4698.700528</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4384.175055</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4597.723099</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4566.98046</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4688.504248</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4585.878064</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4672.920117</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4812.224424</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4704.032891</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4526.50938</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4433.497559</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4503.932012</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4350.067727</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4550.869299</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4616.133679</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4537.503451</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4380.92908</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>4644.916698</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>4689.78266</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>4620.183755</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>4440.109623</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4419.721796</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>4571.54308</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4834.427833</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>4817.801235</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>4820.472521</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>4945.884835</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5065.739314</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>4906.4817</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>4911.706383</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>4902.988087</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>4924.120425</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>4934.693258</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4963.748398</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4833.50362</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4831.12938</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4729.970165</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4726.684146</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4725.833259</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4759.386731</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5009.782899</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5011.991399</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>5121.537837</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>5055.1222</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4878.922013</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4917.137442</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>5032.95801</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5007.101461</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4906.341643</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>5008.145963</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5122.13764</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5150.438386</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4999.086645</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4990.887373</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5034.788273</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5078.154606</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4951.02037</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4995.629678</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4973.678764</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4972.850225</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>5106.070788</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4955.392314</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4903.592506</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5025.613493</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>4935.089122</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4977.879177</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>4620.066645</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>4579.45185</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>4619.67227</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>4713.653844</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>4853.108963</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>4753.314512</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>4737.801022</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>4743.255407</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>4689.826486</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>4441.800164</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>4568.659155</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>4520.690491</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>4504.611728</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4367.665668</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4419.999558</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4437.185282</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>4751.13508</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>4692.577119</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>4744.533438</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>4977.384542</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>4858.223811</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4721.727778</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>4778.684275</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4814.741117</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4786.181295</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4786.348861</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4836.167949</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4692.865769</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4704.744679</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4770.907372</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4839.960009</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4812.084116</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4910.765569</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4829.577423</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>4663.967644</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4649.870664</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>4739.295322</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4743.282342</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4898.589691</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4696.972762</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>4716.981692</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>4738.980267</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>4592.110636</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>4626.154353</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>4816.830015</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4857.304933</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>4934.072876</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4964.606442</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>4971.78271</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>5109.667303</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>5051.717141</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>4987.484493</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4939.129654</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>4819.277591</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>5093.068335</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>5068.023374</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>4988.75482</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>4981.187715</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>5080.530265</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>5108.924991</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>5099.992586</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>5270.736397</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>5232.621863</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>5124.278366</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>5175.131518</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>5046.340366</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>5044.706308</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>4981.485406</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4983.353289</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>5004.122654</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>5096.41785</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>4990.629407</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4999.861587</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>4995.442149</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4886.511361</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4866.369923</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>4851.051826</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>4973.169352</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>4850.310435</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4950.696535</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>4887.531865</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>4944.874694</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>4807.161978</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>4923.634571</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>4921.199456</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4863.319565</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4911.275406</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4867.144773</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4841.626749</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4872.98433</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4968.439963</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>5024.657205</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>5001.896259</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4767.201046</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4916.836573</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4875.469733</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4848.57744</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4908.998204</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4769.007246</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4828.672018</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>4856.973705</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>4692.736593</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4696.680823</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>4720.148736</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>4501.286056</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>4466.173457</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>4543.32779</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4523.909382</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>4629.274348</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>4740.384764</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>4706.049692</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>4597.023332</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4654.418005</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>4636.027068</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>4533.867662</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4491.771081</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>4633.770518</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>4627.060894</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>4650.960926</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>4650.083</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>4585.832407</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>4468.574389</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>4494.447898</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4538.756475</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>4410.657125</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>4428.051637</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>4545.939343</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>4435.495346</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>4462.652581</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4451.253961</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4359.599515</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4433.537562</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>4585.013176</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4580.928588</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>4595.839889</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>4390.689974</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>4453.232433</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4279.726315</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>4607.903126</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4539.5081</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>4445.885477</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>4380.042364</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>4300.796452</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4305.797346</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4212.193852</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4329.09754</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4332.001205</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4484.762476</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4403.178041</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4383.915542</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4277.348998</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>4253.666882</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>4272.83182</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4260.294964</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4319.543315</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>4206.832314</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4265.672054</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>4379.540604</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>4344.398395</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4198.181268</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>4253.369196</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>4169.479865</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>4047.278956</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>4010.990903</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4101.674426</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4092.316495</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>3960.216417</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>4098.382985</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4078.346625</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>4125.753469</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4039.895068</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4020.427767</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4292.251285</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4218.914265</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>4447.620421</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>4457.343308</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>4384.449441</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>4182.82615</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>4173.013291</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>3968.133624</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4142.901931</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4186.211413</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4159.769248</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4185.648343</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4226.249315</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4169.701535</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4205.184045</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4025.630255</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4041.876763</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4243.610293</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4254.866305</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4311.386816</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4380.806145</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4359.291178</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4246.693316</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4212.378742</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4365.035276</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4465.874711</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4483.718822</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4536.512194</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4541.837794</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4451.287089</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4466.475339</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4552.499372</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4519.089742</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4528.054164</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4589.745067</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4636.119931</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4541.532242</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>4592.690633</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4644.938321</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4494.874684</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4577.619284</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4556.498538</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4645.234726</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4637.213369</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4449.732723</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>4436.19345</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>4379.95409</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4453.699781</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4435.968129</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4487.321112</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>4568.042298</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4339.668562</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4345.134729</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4326.713171</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4511.247481</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4606.307538</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4544.789527</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4403.790857</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4433.033679</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4264.37863</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4261.35868</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4129.051358</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4320.223411</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4352.032108</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4512.416655</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4568.646199</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4577.502841</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4589.18258</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4562.31613</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4314.036892</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4334.319814</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4264.853898</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4442.712224</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4455.923962</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4361.205624</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4310.510126</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4209.441177</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4303.394002</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4565.743254</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4636.452845</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4342.618632</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4361.35748</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4269.956826</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4119.478807</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4514.259175</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4695.033178</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4786.826526</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>4684.037393</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>4861.419795</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>4887.515149</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4750.101443</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>5108.512271</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>4836.642834</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4864.004952</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4862.667575</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>5053.813534</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>5016.080028</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>5043.189655</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4877.222567</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>4939.375815</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>4965.734961</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>5116.806908</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>5043.751423</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>4998.400098</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>5210.006142</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>5205.7918</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>5177.731846</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5176.232386</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>5337.053173</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>5340.519207</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>5364.989217</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>5490.293147</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5495.327066</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>5552.076543</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>5386.517958</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>5402.955746</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5473.714677</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>5428.897593</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>5404.946724</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>5455.049293</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5792.19109</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5823.436105</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5678.951355</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>5692.781021</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5572.0376</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5584.30159</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="249189031"/>
+        <c:axId val="906675868"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="249189031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="906675868"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="906675868"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="249189031"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Inference Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$C$1:$C$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>1080.146722</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>614.869427</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>934.746906</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>682.511317</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>394.423246</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>446.752687</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>896.058166</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>804.979534</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>990.079618</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>588.726323</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500.5559</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>701.819797</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>895.103196</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>549.493145</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1217.642063</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>498.72459</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>395.056641</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>510.552688</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>699.06588</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>347.386706</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>801.116481</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>399.653891</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1211.850813</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>584.988136</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>700.105016</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>397.190023</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>700.782036</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1178.565147</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>600.349513</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1191.486794</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>397.702133</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>546.786066</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>895.401409</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>403.638544</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1184.911243</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>706.84393</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>550.250189</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>405.989882</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1094.539185</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>808.806246</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>411.792541</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>704.021961</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>600.306925</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>707.15962</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1033.175498</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>488.539245</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>598.087327</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>680.317722</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>994.561657</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>505.555548</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1097.194498</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>404.370665</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>490.630261</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>501.054951</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>348.299151</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>902.079992</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1272.785295</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>602.789267</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>799.074458</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1201.746737</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>302.173773</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>895.280348</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>399.335116</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>714.447047</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>903.145634</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>600.870201</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>597.090499</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1086.912485</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1167.727321</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>802.577263</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>500.818405</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>903.478764</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>297.320827</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1005.968347</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>402.674279</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>604.295143</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>600.091295</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1100.684975</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>499.540927</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>832.236959</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>706.07071</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1001.850964</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>596.707701</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>803.151978</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>398.366921</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>483.947275</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>555.437619</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>901.913309</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>807.594371</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1202.837297</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>704.961858</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>704.715099</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>702.413088</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>643.95737</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>583.541845</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>698.091091</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>681.483027</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>812.413236</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>498.095039</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>605.315733</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>701.200109</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>403.629933</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>487.102022</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>407.661052</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>508.335152</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>599.667155</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>795.187446</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>779.208593</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1305.580211</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>588.432359</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1406.1713</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>681.096742</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>604.193503</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>397.293665</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>503.283668</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>801.981493</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>612.096809</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>499.218332</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>443.256335</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>498.203816</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>688.103788</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>908.995299</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>591.646913</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>706.493451</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>401.010123</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>514.297264</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>594.909143</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>495.822088</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1102.615766</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>548.373359</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>800.95649</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>395.896516</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>703.946371</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>887.979438</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>397.624245</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>796.250754</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>703.746069</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>454.908283</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>690.39091</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>793.349571</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>712.72496</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>744.383971</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1299.824446</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>594.168705</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>949.489103</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>801.953903</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>599.139442</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>987.608943</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>397.756395</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>302.318953</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>704.141055</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>501.276948</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>1103.942219</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>1071.553518</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>907.439762</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>1198.798383</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1397.99193</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>607.314157</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>590.035977</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>790.904013</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>391.089896</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>714.525177</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>639.208672</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>595.086903</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>594.345064</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>395.066446</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>897.79601</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>696.178257</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>497.637286</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1007.214983</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>710.810901</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>397.02633</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>666.533682</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>521.631798</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>599.4564</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>602.087065</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1087.418867</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>700.900916</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1131.859911</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>576.894917</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>499.597113</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>502.969978</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>698.1017</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>795.128394</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>875.791798</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>496.127532</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>603.269859</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1007.889434</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>498.558648</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>689.526681</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>396.001692</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>400.836583</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>598.263373</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>505.122761</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>607.842439</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>220.69263</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>501.472099</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1299.074435</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>404.067255</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>898.963313</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>801.358962</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>591.617024</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>802.236875</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>704.863527</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>399.101702</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>701.438535</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>495.914776</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>395.479709</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>996.912132</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>1012.995655</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>699.2562</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1298.98358</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>600.111133</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>902.92242</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>698.729266</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>854.867196</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>297.10421</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>1321.213251</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>611.539154</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>584.915736</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>403.835184</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>605.712002</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>493.544925</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>590.440414</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>810.061853</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>704.226528</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>591.826689</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>686.696164</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>894.715696</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>496.50576</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>882.681226</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>600.20353</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>499.36249</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>697.415091</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>602.218321</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>399.016108</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>1065.912367</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>599.539052</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1202.4444</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>499.096142</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>1193.528299</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>707.64441</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>800.384205</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>401.591735</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>551.683002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>590.046509</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>1105.241177</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>802.981763</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>799.62715</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>748.797451</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>955.353421</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>1200.077339</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>794.079554</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>393.308933</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>805.830452</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>600.523875</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>966.258945</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>405.682826</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>892.242558</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>908.175322</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>392.991374</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>554.032671</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>802.222576</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>878.420917</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>399.0971</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>933.128065</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>602.599389</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>593.569751</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>451.766004</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>402.128517</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>1197.288934</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>813.599563</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>698.700054</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>902.665694</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>602.193022</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>311.481573</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>1063.803682</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>383.757927</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>402.802403</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>746.566888</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>598.619291</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>405.03268</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>902.143503</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>597.522588</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>600.086921</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>595.891005</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>802.033576</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>798.071978</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>603.67232</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>689.17971</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>801.016772</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>495.188501</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>801.717433</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>395.998775</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>709.949544</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>804.627074</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>713.243004</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>315.021516</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>797.954706</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>502.327056</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>490.814635</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>900.739526</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>799.690833</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>863.508947</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>1084.879065</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>501.673333</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>392.093143</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>653.076113</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>399.024871</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>603.48642</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>894.146001</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>691.812986</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>824.242643</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>544.159871</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>396.249133</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>510.717835</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>500.473229</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>404.064547</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>803.754767</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>449.701977</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>486.426692</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>604.530491</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>1080.144995</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>496.218631</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>1000.217136</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>444.123892</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>691.950506</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1088.639428</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>505.402808</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>596.0833</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>502.555226</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>991.265555</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>502.080631</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>411.466881</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>518.675638</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>499.565742</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>546.544522</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>404.108029</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>299.134699</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>793.258453</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>798.136897</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>508.916714</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>499.140624</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>490.432381</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>605.810901</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>607.449656</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>493.384978</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>550.877561</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>405.019072</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>768.984877</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>990.750335</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>586.33964</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>399.776225</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>506.468323</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>489.933961</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>446.531504</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>903.720781</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>838.736827</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>418.433139</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>800.563251</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>303.612069</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>452.390507</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>711.41138</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>398.196597</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>696.096272</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>649.179347</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>807.773635</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>697.612356</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>764.244545</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>730.031972</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>699.349439</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>649.619462</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>401.413514</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>696.7488</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>605.921736</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>893.493101</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>499.155998</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>681.029243</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>450.251182</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>498.642125</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>706.114445</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>425.192349</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>600.672467</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>816.301434</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>810.892174</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>497.835811</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>622.612184</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>575.595022</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>698.504168</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>793.217705</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>853.405713</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>1013.984783</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>797.656365</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>687.632803</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>697.154998</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>499.835727</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>705.136525</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>449.602926</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>815.409532</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>793.562361</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>884.029133</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>595.904088</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>514.376027</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>744.908841</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>498.722794</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>401.467919</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>1011.494939</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>699.013285</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>600.768718</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>342.89641</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>918.398104</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>402.476602</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>398.800474</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>853.397573</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>516.703088</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>649.383348</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>583.320271</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>597.563027</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>494.3653</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>792.639189</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>583.93496</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>601.554671</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>405.106945</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>454.615164</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>489.485526</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>901.633956</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>294.935133</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>494.476883</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>397.168566</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>998.799947</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>996.695044</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>792.692418</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>700.192236</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>656.518729</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>580.931353</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>467.655396</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>603.362228</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>395.372508</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>602.690181</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>502.341883</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>1008.747981</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>1002.970412</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>543.616863</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>500.526265</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>711.307934</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>1027.240571</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>699.666827</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>551.098805</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>401.828164</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>1285.906143</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1200.15973</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>888.287828</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>710.247061</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>896.849944</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>952.791969</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>1099.775445</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>892.098581</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>796.720837</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>799.729033</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>844.811608</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>975.131753</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>1406.046346</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>704.56455</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>548.265292</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>512.746509</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>602.755351</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>599.341409</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>924.218075</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>746.461035</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>878.406444</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>392.933366</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>1000.881619</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>851.323869</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>899.215438</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>400.548236</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>797.071093</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>1014.984976</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>1092.118307</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>707.805748</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>994.402545</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>747.998163</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>891.294898</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>699.473912</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>400.040127</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>1014.547364</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>799.974589</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>710.384664</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>403.414989</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>790.960813</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>1106.297622</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>1310.03831</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>400.559338</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>699.890594</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>705.631205</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>888.816442</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>708.265976</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>410.544032</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="964329992"/>
+        <c:axId val="440430489"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="964329992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="440430489"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="440430489"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="964329992"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$D$1:$D$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>1107.917777</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>637.98187</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>958.695561</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>701.456571</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>724.258863</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>891.789389</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1400.393244</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1425.034642</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1624.492035</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1262.112514</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1201.260119</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1400.045673</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1764.32898</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1658.476139</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2316.150608</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1585.044389</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1497.865006</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1705.892192</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1977.259523</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1800.096013</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2163.592377</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1780.593121</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2631.794043</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2069.331361</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2315.588015</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2043.971932</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2379.365724</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3034.871335</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2485.535243</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3056.259346</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2270.122242</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2607.07036</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3074.341687</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2573.779923</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3422.361269</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3058.145039</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3026.808488</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2880.137783</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3812.380731</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3582.419947</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3296.063962</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3558.90736</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3481.716815</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3529.781616</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4121.714053</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3489.225321</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3813.100247</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3910.204202</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4188.427473</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3835.486408</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4420.214979</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3729.219391</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4142.738291</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>4280.518023</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4103.096068</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4604.620767</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5079.769327</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4663.21697</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>4793.729985</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5169.312455</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4390.469261</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5037.73464</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4745.797141</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5084.437326</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5367.563812</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5235.833106</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5200.683419</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5847.720493</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6005.248397</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5692.10089</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5451.921869</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>6008.432754</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5338.306943</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6059.146718</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5537.765078</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5624.409514</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5602.914529</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6181.337066</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5582.516995</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6022.881998</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5816.471917</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6074.115764</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5712.592086</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5893.84593</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5476.273841</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5774.523236</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5928.763768</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>6049.246782</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5962.148082</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6165.965131</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5854.856618</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5774.838823</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5771.71164</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5724.061005</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5882.164842</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5671.671218</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5744.917013</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5952.56198</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5600.868313</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5823.050045</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5935.180219</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5342.653313</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5545.094468</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5346.341823</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5462.7035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5600.39065</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5748.70077</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5762.541967</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6338.706539</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5484.842618</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6340.827991</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5542.228343</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5580.185372</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5461.576553</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5425.964567</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5712.375137</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5541.162977</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5495.787676</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5379.547441</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5431.69334</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5570.99066</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5966.407223</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5609.471944</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5651.17484</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5079.941509</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5046.87056</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>5218.879469</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5305.063643</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5742.37697</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>5229.821153</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>5445.128542</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5062.350375</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5372.555018</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5620.569466</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4812.0229</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5411.038153</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5295.050529</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5158.351631</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5306.988574</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5479.765188</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5551.352584</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5481.887962</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5858.306826</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5042.890764</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5468.883815</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>5171.16093</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>5167.598041</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>5629.200322</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>5075.397946</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4703.688533</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>5372.465553</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>5226.574908</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5739.334174</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5529.332741</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>5345.901358</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5798.450463</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>6250.478663</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5459.934292</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5577.008398</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5776.273248</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5487.15771</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>5646.567877</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>5582.131055</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5540.26689</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5547.529689</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>5348.211304</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>5906.284708</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>5576.623677</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5347.741266</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>5757.888148</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>5458.974747</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>5152.775289</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>5440.967813</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5560.979497</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5644.979199</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>5743.626202</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>6156.938767</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>5623.025329</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>6066.061153</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>5635.665827</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5524.109074</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5451.863321</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>5722.104863</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5940.242734</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>6041.847384</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5544.459477</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5623.906432</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>6062.725207</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5601.743254</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>5657.459251</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>5410.93767</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>5417.230547</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>5589.856998</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>5629.426049</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>5578.872253</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>5148.923636</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5545.187692</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>6253.871757</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>5398.286832</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>5549.824058</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5418.437012</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>5227.520094</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>5545.077019</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>5585.81949</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>5182.472014</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>5462.058057</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>5302.164483</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>5112.055595</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>5459.015496</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>5623.69981</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>5239.502891</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>5827.781208</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4980.144701</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>5335.774378</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>5155.940748</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>5626.578976</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>5004.532729</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>6079.350389</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>5612.355796</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>5456.615047</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>5145.646262</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>5401.722577</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>5320.783942</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>5388.051509</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>5616.319714</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>5559.626677</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>5306.467358</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>5413.833243</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>5680.792868</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>5364.002469</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>5742.887642</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>5534.222299</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>5343.950113</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>5377.163635</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>5268.840885</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>5158.00513</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>5825.576509</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>5525.276343</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>5922.437962</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>5240.998134</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>5948.040266</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>5329.199246</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>5443.006858</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>5248.64625</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>5425.192135</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>5544.705585</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>6085.861819</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>5790.333273</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>5929.793753</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>5819.255992</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>5967.322314</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>6214.466393</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>5656.571445</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>5503.652668</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>5889.063626</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>5616.316695</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>5984.96696</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>5502.235091</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>6019.249849</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>6037.153808</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>5683.839071</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>5807.532234</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>5953.846542</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>6090.588435</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>5472.990166</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>6022.712273</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>5616.593295</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>5603.17204</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>5473.393658</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>5546.426867</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>6230.816041</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>5836.82775</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>5722.946503</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>5826.850455</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>5484.837145</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>5190.565499</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>6062.977234</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>5363.657062</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>5372.922138</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>5663.966953</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>5560.282485</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>5246.051158</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>5848.267074</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>5543.586444</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>5480.136386</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>5541.341711</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>5710.547949</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>5659.135127</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>5493.05465</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>5673.717073</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>5854.924177</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>5518.50686</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>5704.421079</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>5331.836948</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>5617.961777</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>5670.552214</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>5651.928008</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>5100.965462</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>5676.465624</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>5376.014161</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>5202.106928</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>5628.774649</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>5554.511969</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>5385.435203</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>5572.487722</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>5065.916623</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4945.792125</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>5298.205061</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>5167.237235</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>5326.670712</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>5530.762733</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>5363.439891</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>5476.603511</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>5109.418433</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4915.197814</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>5162.697253</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>5143.241723</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>5080.018973</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>5477.886467</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>5066.844784</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>4970.784281</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>5132.360889</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>5634.17177</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>4925.685356</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>5446.408673</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>5016.480735</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>5144.182252</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>5568.112009</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4983.248769</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4973.897115</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4960.754088</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>5593.874931</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>5100.870019</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>5030.77317</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>4937.661912</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>4969.181675</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4858.962037</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>5029.627155</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4862.303699</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>5255.21223</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>5216.290861</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>4846.867766</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4821.12837</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4721.732233</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4951.512941</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4962.211861</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4999.839254</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4975.979202</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4806.710814</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>5081.952375</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>5262.935117</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>4904.01326</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4676.418189</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4849.001438</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>4715.114975</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4732.260658</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>5308.188085</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>5225.761022</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4642.974507</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>5075.153747</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>4489.141534</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>4543.319163</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>4764.830983</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4533.058623</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4817.149367</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>4624.850664</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>4938.22692</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4790.394381</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>4918.253614</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4785.26854</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4747.627606</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4960.609347</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4635.308579</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>5168.269121</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>5080.471044</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>5306.049642</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>4697.117948</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>4871.022034</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>4431.463006</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4677.561156</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4903.030358</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4611.213197</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4808.71511</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>5062.191949</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>5013.830009</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4712.922956</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4657.589739</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4629.124685</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4964.366961</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>5064.50961</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>5176.104029</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>5419.510728</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>5171.111943</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4949.904119</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4931.84874</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4875.460703</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>5190.323736</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4945.576048</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>5361.511626</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>5357.360055</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>5344.599022</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>5073.199927</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>5083.799599</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>5277.437983</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>5037.352658</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>5013.309886</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>5657.34967</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>5256.118527</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>5209.925351</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>5001.535831</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>5427.299688</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4998.344386</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4969.354912</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>5518.803799</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>5164.023357</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>5112.637571</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>5033.312321</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>5026.782717</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4965.512281</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>5246.361518</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>5112.594372</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>5186.918069</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4764.248707</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4828.456993</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4837.039897</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>5438.968537</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4923.083771</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>5052.00351</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4817.551223</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>5447.275726</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>5285.183774</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>5069.340198</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4847.289594</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4996.35794</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4947.036761</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4999.445851</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>5296.523927</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4983.790249</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>5205.814361</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>5084.254313</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>5342.927573</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>5364.853526</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4825.163561</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4967.791989</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>5176.855596</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>5482.400895</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>5022.972153</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4772.764282</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4720.877066</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>5864.797497</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>5848.859875</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>5247.25456</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>5093.529841</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>5177.40667</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>5081.425276</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>5624.81332</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>5602.021759</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>5600.498463</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>5493.137526</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>5717.404103</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>5882.304502</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>6165.798289</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>5824.027021</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>5394.498326</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>5388.021761</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>5476.689526</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>5668.053243</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>5951.638603</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>5813.22619</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>5766.066311</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>5343.715981</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>5990.29248</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>5980.852977</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>5952.628761</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>5418.436534</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>6017.888935</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>6232.089976</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>6283.623253</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5894.543834</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>6344.275418</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>6100.40917</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>6270.667515</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>6209.033659</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5921.741093</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>6594.837307</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>6205.953147</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>6135.26941</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5889.324366</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>6233.270106</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>6520.284846</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>6783.994203</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>6206.798828</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>6546.680499</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>6400.21366</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>6592.716663</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>6305.104976</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>6007.512822</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="880846525"/>
+        <c:axId val="488675741"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="880846525"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="488675741"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="488675741"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="880846525"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>806450</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>56515</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3263900" y="158750"/>
+        <a:ext cx="7689215" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>863600</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3321050" y="3041650"/>
+        <a:ext cx="7613650" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3384550" y="5905500"/>
+        <a:ext cx="7594600" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3359150" y="8718550"/>
+        <a:ext cx="7613650" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8455,5 +17821,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>